--- a/jacky_code/Matlab_data/FullPower_BeamShutdownSweep_GS01_U50_P03S49_RelayUserCount_OnlyBPLR_vs_SAPR-R.xlsx
+++ b/jacky_code/Matlab_data/FullPower_BeamShutdownSweep_GS01_U50_P03S49_RelayUserCount_OnlyBPLR_vs_SAPR-R.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="417" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="451" uniqueCount="22">
   <si>
     <t>time_segment</t>
   </si>
@@ -74,6 +74,12 @@
   </si>
   <si>
     <t>time_offset_from_worst_epfd_slot_s</t>
+  </si>
+  <si>
+    <t>Only HBR</t>
+  </si>
+  <si>
+    <t>EABR</t>
   </si>
 </sst>
 </file>
@@ -347,9 +353,9 @@
   <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.6640625" customWidth="true"/>
-    <col min="2" max="2" width="9.21875" customWidth="true"/>
-    <col min="3" max="3" width="15.109375" customWidth="true"/>
+    <col min="1" max="1" width="34.140625" customWidth="true"/>
+    <col min="2" max="2" width="9.28515625" customWidth="true"/>
+    <col min="3" max="3" width="16.42578125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -368,7 +374,7 @@
         <v>-60</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C2" s="0">
         <v>0</v>
@@ -379,7 +385,7 @@
         <v>-40</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C3" s="0">
         <v>10.214285714285714</v>
@@ -390,7 +396,7 @@
         <v>-20</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C4" s="0">
         <v>22.399999999999999</v>
@@ -401,7 +407,7 @@
         <v>0</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C5" s="0">
         <v>27.571428571428573</v>
@@ -412,7 +418,7 @@
         <v>20</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C6" s="0">
         <v>20.25</v>
@@ -423,7 +429,7 @@
         <v>40</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C7" s="0">
         <v>8.75</v>
@@ -434,7 +440,7 @@
         <v>60</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C8" s="0">
         <v>0</v>
@@ -445,7 +451,7 @@
         <v>-60</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C9" s="0">
         <v>0</v>
@@ -456,7 +462,7 @@
         <v>-40</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C10" s="0">
         <v>13.285714285714286</v>
@@ -467,7 +473,7 @@
         <v>-20</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C11" s="0">
         <v>33.649999999999999</v>
@@ -478,7 +484,7 @@
         <v>0</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C12" s="0">
         <v>43.857142857142854</v>
@@ -489,7 +495,7 @@
         <v>20</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C13" s="0">
         <v>33.25</v>
@@ -500,7 +506,7 @@
         <v>40</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C14" s="0">
         <v>12.3125</v>
@@ -511,7 +517,7 @@
         <v>60</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C15" s="0">
         <v>0</v>
